--- a/artfynd/A 10723-2023 artfynd.xlsx
+++ b/artfynd/A 10723-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10723-2023 artfynd.xlsx
+++ b/artfynd/A 10723-2023 artfynd.xlsx
@@ -10218,7 +10218,7 @@
         <v>107930207</v>
       </c>
       <c r="B84" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>

--- a/artfynd/A 10723-2023 artfynd.xlsx
+++ b/artfynd/A 10723-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107929149</v>
+        <v>107929082</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oppdalsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368471.0011369271</v>
+        <v>368469</v>
       </c>
       <c r="R2" t="n">
-        <v>7017903.532331052</v>
+        <v>7017894</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,24 +744,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkad gran.</t>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107928990</v>
+        <v>107929174</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,40 +789,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oppdalsvallen, Jmt</t>
+          <t>Oppdalsvallen S, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368467.3867121469</v>
+        <v>368491</v>
       </c>
       <c r="R3" t="n">
-        <v>7017870.325649522</v>
+        <v>7017893</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,24 +847,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,49 +864,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107929082</v>
+        <v>107929162</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368468.3250093604</v>
+        <v>368471</v>
       </c>
       <c r="R4" t="n">
-        <v>7017893.274856338</v>
+        <v>7017904</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,24 +945,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107929331</v>
+        <v>107928990</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368604.2119650252</v>
+        <v>368467</v>
       </c>
       <c r="R5" t="n">
-        <v>7017894.032147422</v>
+        <v>7017871</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,19 +1048,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1162,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107929174</v>
+        <v>107929149</v>
       </c>
       <c r="B6" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,35 +1093,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oppdalsvallen S, Jmt</t>
+          <t>Oppdalsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>368491.3238309235</v>
+        <v>368471</v>
       </c>
       <c r="R6" t="n">
-        <v>7017892.785346957</v>
+        <v>7017904</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,19 +1156,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,27 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107929162</v>
+        <v>107929331</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,35 +1201,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oppdalsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>368471.0011369271</v>
+        <v>368605</v>
       </c>
       <c r="R7" t="n">
-        <v>7017903.532331052</v>
+        <v>7017894</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1349,19 +1264,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,53 +1298,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89567452</v>
+        <v>107928712</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Oppdalsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369012.1632423563</v>
+        <v>368508</v>
       </c>
       <c r="R8" t="n">
-        <v>7017848.098242089</v>
+        <v>7017670</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,22 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,31 +1389,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89567453</v>
+        <v>107928779</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,37 +1412,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Oppdalsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>369000.8548410241</v>
+        <v>368518</v>
       </c>
       <c r="R9" t="n">
-        <v>7017891.828914016</v>
+        <v>7017706</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,22 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,35 +1487,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>89567441</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1660,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>369011.1813057118</v>
+        <v>369011</v>
       </c>
       <c r="R10" t="n">
-        <v>7017835.06689981</v>
+        <v>7017835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,19 +1567,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,16 +1603,11 @@
         <v>107929632</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1777,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>368974.1724255448</v>
+        <v>368974</v>
       </c>
       <c r="R11" t="n">
-        <v>7017801.867082651</v>
+        <v>7017802</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1810,19 +1669,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,51 +1698,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107929598</v>
+        <v>107929715</v>
       </c>
       <c r="B12" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oppdalsvallen SÖ, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>368974.1724255448</v>
+        <v>368983</v>
       </c>
       <c r="R12" t="n">
-        <v>7017801.867082651</v>
+        <v>7017821</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,19 +1767,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,27 +1784,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107929715</v>
+        <v>89567453</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,38 +1807,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>368983.0713931847</v>
+        <v>369001</v>
       </c>
       <c r="R13" t="n">
-        <v>7017820.886479281</v>
+        <v>7017892</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,22 +1861,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,27 +1881,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>107929588</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>368954.4586866212</v>
+        <v>368955</v>
       </c>
       <c r="R14" t="n">
-        <v>7017783.28808958</v>
+        <v>7017784</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2154,19 +1971,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2198,15 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89567758</v>
+        <v>107929598</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,37 +2016,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Oppdalsvallen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>368484.857163461</v>
+        <v>368974</v>
       </c>
       <c r="R15" t="n">
-        <v>7017568.95511037</v>
+        <v>7017802</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2268,22 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,69 +2091,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89567772</v>
+        <v>107928595</v>
       </c>
       <c r="B16" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Oppdalsvallen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>368503.9037055164</v>
+        <v>368499</v>
       </c>
       <c r="R16" t="n">
-        <v>7017560.062581494</v>
+        <v>7017585</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2384,22 +2169,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,62 +2195,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89567741</v>
+        <v>89567758</v>
       </c>
       <c r="B17" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2475,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>368439.1493151461</v>
+        <v>368485</v>
       </c>
       <c r="R17" t="n">
-        <v>7017577.134687535</v>
+        <v>7017569</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,19 +2279,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,12 +2315,7 @@
         <v>107928718</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>368499.0569723834</v>
+        <v>368499</v>
       </c>
       <c r="R18" t="n">
-        <v>7017585.053529237</v>
+        <v>7017585</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2625,19 +2381,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,54 +2410,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107928595</v>
+        <v>89567741</v>
       </c>
       <c r="B19" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oppdalsvallen, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>368499.0569723834</v>
+        <v>368439</v>
       </c>
       <c r="R19" t="n">
-        <v>7017585.053529237</v>
+        <v>7017577</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2735,22 +2475,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,71 +2495,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107927222</v>
+        <v>89567778</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oppdalsbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>368443.7931941936</v>
+        <v>368633</v>
       </c>
       <c r="R20" t="n">
-        <v>7017547.193226356</v>
+        <v>7017448</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2853,27 +2576,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,27 +2596,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89567460</v>
+        <v>89567772</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,21 +2623,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2940,10 +2647,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>369121.9090737468</v>
+        <v>368504</v>
       </c>
       <c r="R21" t="n">
-        <v>7017550.190839273</v>
+        <v>7017560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,21 +2680,11 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2996,6 +2693,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3016,15 +2718,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89567751</v>
+        <v>107927222</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3032,37 +2729,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Oppdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>369065.1490959969</v>
+        <v>368444</v>
       </c>
       <c r="R22" t="n">
-        <v>7017331.162186393</v>
+        <v>7017548</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3086,22 +2789,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,31 +2814,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89567766</v>
+        <v>107932488</v>
       </c>
       <c r="B23" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,37 +2837,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>368945.8241139695</v>
+        <v>369217</v>
       </c>
       <c r="R23" t="n">
-        <v>7017382.903446846</v>
+        <v>7017394</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3202,22 +2892,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,31 +2912,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89567792</v>
+        <v>113250172</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,37 +2935,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>369269.0985576868</v>
+        <v>369067</v>
       </c>
       <c r="R24" t="n">
-        <v>7017151.108716546</v>
+        <v>7016776</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3318,22 +2989,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,69 +3019,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89567457</v>
+        <v>107930861</v>
       </c>
       <c r="B25" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>389</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>369431.1939696531</v>
+        <v>369408</v>
       </c>
       <c r="R25" t="n">
-        <v>7017363.171310367</v>
+        <v>7017513</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3434,22 +3101,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst i aspklon.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3464,31 +3126,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89567440</v>
+        <v>107930155</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,37 +3149,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>369309.1976004342</v>
+        <v>369285</v>
       </c>
       <c r="R26" t="n">
-        <v>7017415.908194422</v>
+        <v>7017716</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3550,22 +3204,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3580,69 +3224,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89567431</v>
+        <v>107930536</v>
       </c>
       <c r="B27" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>369072.8144175367</v>
+        <v>369405</v>
       </c>
       <c r="R27" t="n">
-        <v>7017563.90837601</v>
+        <v>7017541</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3666,22 +3302,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3696,31 +3322,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89567433</v>
+        <v>107930878</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,37 +3345,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>369166.7928273273</v>
+        <v>369408</v>
       </c>
       <c r="R28" t="n">
-        <v>7017754.813357852</v>
+        <v>7017513</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3782,22 +3400,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3812,31 +3420,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89567775</v>
+        <v>107932699</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,37 +3443,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>368945.9524266618</v>
+        <v>369219</v>
       </c>
       <c r="R29" t="n">
-        <v>7017386.053818856</v>
+        <v>7017411</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3898,27 +3498,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3933,31 +3518,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89567446</v>
+        <v>107934103</v>
       </c>
       <c r="B30" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3965,37 +3541,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>369207.0073310379</v>
+        <v>368957</v>
       </c>
       <c r="R30" t="n">
-        <v>7017755.882691351</v>
+        <v>7017205</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4019,22 +3596,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4049,31 +3616,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89567432</v>
+        <v>113250173</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4081,37 +3639,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>368806.8951408337</v>
+        <v>369072</v>
       </c>
       <c r="R31" t="n">
-        <v>7017618.014495844</v>
+        <v>7016708</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4135,27 +3693,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4170,31 +3723,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89567462</v>
+        <v>113250174</v>
       </c>
       <c r="B32" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,37 +3746,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>369184.9020923725</v>
+        <v>369082</v>
       </c>
       <c r="R32" t="n">
-        <v>7017745.062049226</v>
+        <v>7016726</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4256,22 +3800,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4286,31 +3830,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89567795</v>
+        <v>89567451</v>
       </c>
       <c r="B33" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4342,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>369029.8536453465</v>
+        <v>369343</v>
       </c>
       <c r="R33" t="n">
-        <v>7016829.91105915</v>
+        <v>7017406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,19 +3910,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4418,15 +3943,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89567454</v>
+        <v>89567455</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,21 +3954,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4458,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>369129.8672442111</v>
+        <v>369117</v>
       </c>
       <c r="R34" t="n">
-        <v>7017534.991544188</v>
+        <v>7017561</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4491,19 +4011,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4534,15 +4044,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>89567438</v>
+        <v>89567795</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4550,21 +4055,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4574,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>369002.8183772939</v>
+        <v>369030</v>
       </c>
       <c r="R35" t="n">
-        <v>7017563.151281677</v>
+        <v>7016830</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4607,19 +4112,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,37 +4145,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89567461</v>
+        <v>89567445</v>
       </c>
       <c r="B36" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4690,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>369030.9706853617</v>
+        <v>369240</v>
       </c>
       <c r="R36" t="n">
-        <v>7017556.145130774</v>
+        <v>7017754</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4723,21 +4213,11 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4746,6 +4226,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Björklåga</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4766,15 +4251,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89567445</v>
+        <v>107929983</v>
       </c>
       <c r="B37" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4800,19 +4280,20 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>369239.8839218214</v>
+        <v>369253</v>
       </c>
       <c r="R37" t="n">
-        <v>7017754.095545859</v>
+        <v>7017720</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4836,22 +4317,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4862,40 +4333,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Björklåga</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89567447</v>
+        <v>107930671</v>
       </c>
       <c r="B38" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4903,37 +4360,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>369072.0413249766</v>
+        <v>369403</v>
       </c>
       <c r="R38" t="n">
-        <v>7017567.095245832</v>
+        <v>7017509</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4957,22 +4415,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4987,31 +4435,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89567455</v>
+        <v>107931511</v>
       </c>
       <c r="B39" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5019,37 +4458,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>369116.9407115439</v>
+        <v>369323</v>
       </c>
       <c r="R39" t="n">
-        <v>7017561.211511472</v>
+        <v>7017420</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5073,22 +4513,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5103,69 +4533,61 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89567737</v>
+        <v>107932057</v>
       </c>
       <c r="B40" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Snasahögarna, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>368952.8514980184</v>
+        <v>369277</v>
       </c>
       <c r="R40" t="n">
-        <v>7017378.109231457</v>
+        <v>7017448</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5189,22 +4611,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5219,53 +4636,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89567748</v>
+        <v>89567431</v>
       </c>
       <c r="B41" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5275,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>368956.1819085664</v>
+        <v>369073</v>
       </c>
       <c r="R41" t="n">
-        <v>7017371.211580575</v>
+        <v>7017564</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5308,19 +4716,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5351,37 +4749,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>89567794</v>
+        <v>89567737</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5391,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>368990.8943181796</v>
+        <v>368953</v>
       </c>
       <c r="R42" t="n">
-        <v>7017358.978824864</v>
+        <v>7017378</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5424,21 +4817,11 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5447,11 +4830,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Färska ringhack i gran</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5472,37 +4850,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>89567439</v>
+        <v>89567433</v>
       </c>
       <c r="B43" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5512,10 +4885,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>368845.0650747413</v>
+        <v>369167</v>
       </c>
       <c r="R43" t="n">
-        <v>7017579.945821211</v>
+        <v>7017755</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5545,19 +4918,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5588,37 +4951,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>89567444</v>
+        <v>89567438</v>
       </c>
       <c r="B44" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5628,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>368995.1757868837</v>
+        <v>369003</v>
       </c>
       <c r="R44" t="n">
-        <v>7017563.913229365</v>
+        <v>7017563</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5661,19 +5019,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5704,37 +5052,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>89567448</v>
+        <v>89567454</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5744,10 +5087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>369168.9180010961</v>
+        <v>369130</v>
       </c>
       <c r="R45" t="n">
-        <v>7017485.170000658</v>
+        <v>7017535</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5777,19 +5120,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5823,16 +5156,11 @@
         <v>89567783</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5860,10 +5188,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>368948.9421256157</v>
+        <v>368949</v>
       </c>
       <c r="R46" t="n">
-        <v>7017381.87485372</v>
+        <v>7017382</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5893,19 +5221,9 @@
           <t>2020-08-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5936,59 +5254,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>107929843</v>
+        <v>89567792</v>
       </c>
       <c r="B47" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>369201.3641227403</v>
+        <v>369269</v>
       </c>
       <c r="R47" t="n">
-        <v>7017783.607428506</v>
+        <v>7017151</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6012,27 +5319,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6047,49 +5339,48 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>107931511</v>
+        <v>107929944</v>
       </c>
       <c r="B48" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6100,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>369322.9185223287</v>
+        <v>369262</v>
       </c>
       <c r="R48" t="n">
-        <v>7017420.309613964</v>
+        <v>7017760</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6133,19 +5424,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6172,60 +5453,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>107930631</v>
+        <v>107930181</v>
       </c>
       <c r="B49" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>369384.5250429783</v>
+        <v>369285</v>
       </c>
       <c r="R49" t="n">
-        <v>7017536.814427076</v>
+        <v>7017716</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6255,19 +5522,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6282,68 +5539,58 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>107926663</v>
+        <v>107931518</v>
       </c>
       <c r="B50" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Snasahögarna V, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>369067.6329521956</v>
+        <v>369323</v>
       </c>
       <c r="R50" t="n">
-        <v>7016637.647899015</v>
+        <v>7017420</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6373,19 +5620,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6400,49 +5637,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>107930536</v>
+        <v>107933004</v>
       </c>
       <c r="B51" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6453,10 +5685,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>369404.121985073</v>
+        <v>369172</v>
       </c>
       <c r="R51" t="n">
-        <v>7017541.428207901</v>
+        <v>7017356</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6486,19 +5718,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6518,44 +5740,39 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>107929983</v>
+        <v>107934096</v>
       </c>
       <c r="B52" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6566,10 +5783,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>369252.913724056</v>
+        <v>368957</v>
       </c>
       <c r="R52" t="n">
-        <v>7017719.30923225</v>
+        <v>7017205</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6599,19 +5816,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6631,22 +5838,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>107934103</v>
+        <v>89567446</v>
       </c>
       <c r="B53" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6654,38 +5856,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>368956.6294816291</v>
+        <v>369207</v>
       </c>
       <c r="R53" t="n">
-        <v>7017204.843350253</v>
+        <v>7017756</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6709,22 +5910,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6739,27 +5930,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>107929855</v>
+        <v>89567766</v>
       </c>
       <c r="B54" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,38 +5957,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>369201.3641227403</v>
+        <v>368946</v>
       </c>
       <c r="R54" t="n">
-        <v>7017783.607428506</v>
+        <v>7017383</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6822,22 +6011,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6852,27 +6031,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>107932488</v>
+        <v>107931475</v>
       </c>
       <c r="B55" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,21 +6058,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6905,10 +6083,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>369217.1212063232</v>
+        <v>369333</v>
       </c>
       <c r="R55" t="n">
-        <v>7017393.954171305</v>
+        <v>7017442</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6938,19 +6116,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6965,27 +6133,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>107933310</v>
+        <v>107932217</v>
       </c>
       <c r="B56" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6993,40 +6156,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>369131.536522561</v>
+        <v>369299</v>
       </c>
       <c r="R56" t="n">
-        <v>7017465.052549496</v>
+        <v>7017387</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7056,19 +6214,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7083,27 +6231,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>107932057</v>
+        <v>89567432</v>
       </c>
       <c r="B57" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7111,38 +6254,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>369277.5791544355</v>
+        <v>368807</v>
       </c>
       <c r="R57" t="n">
-        <v>7017448.747807737</v>
+        <v>7017618</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7166,27 +6308,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7201,27 +6333,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>107932217</v>
+        <v>89567736</v>
       </c>
       <c r="B58" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7229,38 +6360,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>369299.4467623886</v>
+        <v>369311</v>
       </c>
       <c r="R58" t="n">
-        <v>7017387.002726176</v>
+        <v>7017095</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7284,22 +6414,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7314,27 +6439,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>107930155</v>
+        <v>89567775</v>
       </c>
       <c r="B59" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7342,38 +6466,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>369285.2669369324</v>
+        <v>368946</v>
       </c>
       <c r="R59" t="n">
-        <v>7017715.740838028</v>
+        <v>7017386</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7397,22 +6520,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7427,27 +6545,26 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>107931518</v>
+        <v>89567794</v>
       </c>
       <c r="B60" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7455,38 +6572,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>369322.9185223287</v>
+        <v>368991</v>
       </c>
       <c r="R60" t="n">
-        <v>7017420.309613964</v>
+        <v>7017359</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7510,22 +6626,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7536,31 +6642,35 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Färska ringhack i gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>107930671</v>
+        <v>107926663</v>
       </c>
       <c r="B61" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7568,35 +6678,40 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna V, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>369402.770258002</v>
+        <v>369068</v>
       </c>
       <c r="R61" t="n">
-        <v>7017508.125771915</v>
+        <v>7016637</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7626,19 +6741,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7653,67 +6758,63 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>107930861</v>
+        <v>107926893</v>
       </c>
       <c r="B62" t="n">
-        <v>78477</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>389</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna V, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>369408.8478870493</v>
+        <v>368988</v>
       </c>
       <c r="R62" t="n">
-        <v>7017513.288405519</v>
+        <v>7016778</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7743,24 +6844,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst i aspklon.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7780,22 +6866,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>107934096</v>
+        <v>107929843</v>
       </c>
       <c r="B63" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7803,35 +6884,40 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>368956.6294816291</v>
+        <v>369202</v>
       </c>
       <c r="R63" t="n">
-        <v>7017204.843350253</v>
+        <v>7017784</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7861,19 +6947,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7888,27 +6969,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>107930356</v>
+        <v>107930207</v>
       </c>
       <c r="B64" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7933,11 +7009,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7946,13 +7026,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>369361.171267083</v>
+        <v>369259</v>
       </c>
       <c r="R64" t="n">
-        <v>7017617.548423229</v>
+        <v>7017626</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7979,19 +7059,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ivrigt lockande.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8018,15 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>107931475</v>
+        <v>107930311</v>
       </c>
       <c r="B65" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8034,35 +7104,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>369333.7103379557</v>
+        <v>369323</v>
       </c>
       <c r="R65" t="n">
-        <v>7017441.509186215</v>
+        <v>7017679</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8092,19 +7167,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8119,27 +7189,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>107933730</v>
+        <v>107930356</v>
       </c>
       <c r="B66" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8177,10 +7242,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>369028.8422527594</v>
+        <v>369362</v>
       </c>
       <c r="R66" t="n">
-        <v>7017359.688010616</v>
+        <v>7017618</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8210,19 +7275,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8242,22 +7297,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>107933374</v>
+        <v>107933310</v>
       </c>
       <c r="B67" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8265,35 +7315,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>369093.8066765376</v>
+        <v>369131</v>
       </c>
       <c r="R67" t="n">
-        <v>7017436.384526047</v>
+        <v>7017465</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8323,19 +7378,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8362,15 +7407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>107934217</v>
+        <v>107933559</v>
       </c>
       <c r="B68" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8408,10 +7448,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>368904.7459964011</v>
+        <v>369062</v>
       </c>
       <c r="R68" t="n">
-        <v>7017128.061301586</v>
+        <v>7017390</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8441,19 +7481,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8480,15 +7510,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>107933828</v>
+        <v>107933730</v>
       </c>
       <c r="B69" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8496,35 +7521,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>369044.2937014909</v>
+        <v>369029</v>
       </c>
       <c r="R69" t="n">
-        <v>7017306.765669475</v>
+        <v>7017359</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8554,19 +7584,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8593,15 +7613,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>107931482</v>
+        <v>107933838</v>
       </c>
       <c r="B70" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8609,35 +7624,40 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>369333.7103379557</v>
+        <v>369045</v>
       </c>
       <c r="R70" t="n">
-        <v>7017441.509186215</v>
+        <v>7017307</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8667,19 +7687,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8699,22 +7709,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>107933559</v>
+        <v>107934086</v>
       </c>
       <c r="B71" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8752,10 +7757,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>369062.5725225214</v>
+        <v>368957</v>
       </c>
       <c r="R71" t="n">
-        <v>7017389.871234985</v>
+        <v>7017205</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8785,19 +7790,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8824,15 +7819,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>107934358</v>
+        <v>107934217</v>
       </c>
       <c r="B72" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8861,7 +7851,7 @@
       <c r="K72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8870,10 +7860,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>368842.2394079106</v>
+        <v>368904</v>
       </c>
       <c r="R72" t="n">
-        <v>7017023.307471964</v>
+        <v>7017129</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8903,24 +7893,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8947,15 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>107929917</v>
+        <v>107934358</v>
       </c>
       <c r="B73" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8963,35 +7933,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>369238.4838427139</v>
+        <v>368842</v>
       </c>
       <c r="R73" t="n">
-        <v>7017764.068815481</v>
+        <v>7017024</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9021,19 +7996,14 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9053,22 +8023,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>107934086</v>
+        <v>113250170</v>
       </c>
       <c r="B74" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9094,22 +8059,21 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>368956.6294816291</v>
+        <v>369046</v>
       </c>
       <c r="R74" t="n">
-        <v>7017204.843350253</v>
+        <v>7016790</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9136,22 +8100,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9178,15 +8142,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>107930311</v>
+        <v>113250178</v>
       </c>
       <c r="B75" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9212,22 +8171,21 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>369322.5945975493</v>
+        <v>369061</v>
       </c>
       <c r="R75" t="n">
-        <v>7017679.065848501</v>
+        <v>7016650</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9254,27 +8212,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9289,27 +8242,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>107926893</v>
+        <v>113250180</v>
       </c>
       <c r="B76" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9335,22 +8283,21 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Snasahögarna V, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>368988.0259472959</v>
+        <v>369108</v>
       </c>
       <c r="R76" t="n">
-        <v>7016778.40966922</v>
+        <v>7016587</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9377,22 +8324,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9419,15 +8366,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>107932699</v>
+        <v>113250183</v>
       </c>
       <c r="B77" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9435,35 +8377,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>369219.1683073569</v>
+        <v>369095</v>
       </c>
       <c r="R77" t="n">
-        <v>7017411.001128756</v>
+        <v>7016480</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9490,22 +8436,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9525,58 +8471,58 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>107930878</v>
+        <v>107932237</v>
       </c>
       <c r="B78" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>369408.8478870493</v>
+        <v>369283</v>
       </c>
       <c r="R78" t="n">
-        <v>7017513.288405519</v>
+        <v>7017398</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9606,19 +8552,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9633,63 +8569,69 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>107929944</v>
+        <v>124269609</v>
       </c>
       <c r="B79" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>369262.7072570403</v>
+        <v>369325</v>
       </c>
       <c r="R79" t="n">
-        <v>7017760.379899688</v>
+        <v>7017599</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9716,22 +8658,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Passerade vägen från norra till södra sidan.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9746,27 +8693,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Ulla Falkdalen, Thomas Holmberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>107933838</v>
+        <v>89567462</v>
       </c>
       <c r="B80" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9774,43 +8716,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>369044.2937014909</v>
+        <v>369185</v>
       </c>
       <c r="R80" t="n">
-        <v>7017306.765669475</v>
+        <v>7017745</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9834,22 +8770,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9864,27 +8790,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>107930568</v>
+        <v>89567745</v>
       </c>
       <c r="B81" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9892,38 +8817,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>369391.4308669949</v>
+        <v>369141</v>
       </c>
       <c r="R81" t="n">
-        <v>7017540.140270015</v>
+        <v>7016416</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9947,22 +8871,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9977,27 +8891,26 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>107933004</v>
+        <v>107930631</v>
       </c>
       <c r="B82" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10005,35 +8918,44 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>369171.7597904818</v>
+        <v>369384</v>
       </c>
       <c r="R82" t="n">
-        <v>7017355.22639049</v>
+        <v>7017537</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10063,19 +8985,9 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10090,27 +9002,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>107930181</v>
+        <v>89567759</v>
       </c>
       <c r="B83" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10118,38 +9025,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>369285.2669369324</v>
+        <v>368840</v>
       </c>
       <c r="R83" t="n">
-        <v>7017715.740838028</v>
+        <v>7017458</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10173,22 +9079,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10203,75 +9099,64 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>107930207</v>
+        <v>89567448</v>
       </c>
       <c r="B84" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Myckelbäcken, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>369259</v>
+        <v>369169</v>
       </c>
       <c r="R84" t="n">
-        <v>7017626</v>
+        <v>7017485</v>
       </c>
       <c r="S84" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10295,17 +9180,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ivrigt lockande.</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10320,65 +9200,64 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113250172</v>
+        <v>89567460</v>
       </c>
       <c r="B85" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>283</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>369067</v>
+        <v>369122</v>
       </c>
       <c r="R85" t="n">
-        <v>7016776</v>
+        <v>7017550</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10402,22 +9281,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10432,65 +9301,64 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113250174</v>
+        <v>89567461</v>
       </c>
       <c r="B86" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>864</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>369082</v>
+        <v>369031</v>
       </c>
       <c r="R86" t="n">
-        <v>7016726</v>
+        <v>7017556</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10514,22 +9382,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10544,27 +9402,26 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113250178</v>
+        <v>107931482</v>
       </c>
       <c r="B87" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10572,39 +9429,35 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
+          <t>Myckelbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>369061</v>
+        <v>369333</v>
       </c>
       <c r="R87" t="n">
-        <v>7016650</v>
+        <v>7017442</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10631,22 +9484,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10666,22 +9509,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113250180</v>
+        <v>113250179</v>
       </c>
       <c r="B88" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81332</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10689,39 +9527,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>229436</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Halmgul örnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ochrolechia alboflavescens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>369108</v>
+        <v>369052</v>
       </c>
       <c r="R88" t="n">
-        <v>7016587</v>
+        <v>7016628</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10753,7 +9586,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10763,7 +9596,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10790,37 +9623,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113250182</v>
+        <v>113250176</v>
       </c>
       <c r="B89" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10830,10 +9658,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>369093</v>
+        <v>369107</v>
       </c>
       <c r="R89" t="n">
-        <v>7016506</v>
+        <v>7016707</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10865,7 +9693,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10875,7 +9703,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10886,6 +9714,21 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10902,15 +9745,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113250170</v>
+        <v>89567457</v>
       </c>
       <c r="B90" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10918,42 +9756,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
+          <t>Snasahögarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>369046</v>
+        <v>369431</v>
       </c>
       <c r="R90" t="n">
-        <v>7016790</v>
+        <v>7017363</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10977,22 +9810,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11007,59 +9830,56 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113250176</v>
+        <v>113292342</v>
       </c>
       <c r="B91" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80341</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
+        <v>6331316</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rostania effusa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>A.Košuth. et al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Snasahögarnas fritidsby V, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>369107</v>
+        <v>369109</v>
       </c>
       <c r="R91" t="n">
         <v>7016707</v>
@@ -11092,19 +9912,14 @@
           <t>2023-11-14</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2023-11-14</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:36</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Steril bål.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11113,9 +9928,15 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Fjällnära kontinuitetsbarrskog med inslag av björk och asp.</t>
+        </is>
+      </c>
       <c r="AJ91" t="inlineStr">
         <is>
           <t>asp</t>
@@ -11126,12 +9947,26 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AT91" t="inlineStr"/>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="AW91" t="inlineStr">
         <is>
           <t>Johan Råghall</t>
@@ -11143,588 +9978,6 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>113250183</v>
-      </c>
-      <c r="B92" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>369095</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7016480</v>
-      </c>
-      <c r="S92" t="n">
-        <v>25</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>113250173</v>
-      </c>
-      <c r="B93" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>864</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>369072</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7016708</v>
-      </c>
-      <c r="S93" t="n">
-        <v>25</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>113250177</v>
-      </c>
-      <c r="B94" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>369113</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7016686</v>
-      </c>
-      <c r="S94" t="n">
-        <v>25</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>113250179</v>
-      </c>
-      <c r="B95" t="n">
-        <v>80449</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>229436</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Halmgul örnlav</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Ochrolechia alboflavescens</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Wulfen) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Snasahögarnas fritidsby V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>369052</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7016628</v>
-      </c>
-      <c r="S95" t="n">
-        <v>25</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>124269609</v>
-      </c>
-      <c r="B96" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Myckelbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>369325</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7017599</v>
-      </c>
-      <c r="S96" t="n">
-        <v>25</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Passerade vägen från norra till södra sidan.</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Ulla Falkdalen, Thomas Holmberg</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10723-2023 artfynd.xlsx
+++ b/artfynd/A 10723-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929174</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107928990</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929149</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929331</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107928712</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107928779</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567441</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929632</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929715</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567453</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929588</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929598</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107928595</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567758</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107928718</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567741</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567778</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2715,6 +2815,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567772</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107927222</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107932488</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250172</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930861</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3233,6 +3358,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930155</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3331,6 +3461,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930536</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3429,6 +3564,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930878</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107932699</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3625,6 +3770,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107934103</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250173</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3839,6 +3994,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250174</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3940,6 +4100,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567451</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4041,6 +4206,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567455</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4142,6 +4312,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567795</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4248,6 +4423,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567445</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4346,6 +4526,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929983</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4444,6 +4629,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930671</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107931511</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4645,6 +4840,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107932057</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4746,6 +4946,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567431</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4847,6 +5052,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567737</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4948,6 +5158,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567433</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5049,6 +5264,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567438</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5150,6 +5370,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567454</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5251,6 +5476,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567783</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5352,6 +5582,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567792</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5450,6 +5685,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929944</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5548,6 +5788,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930181</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5646,6 +5891,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107931518</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5744,6 +5994,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107933004</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5842,6 +6097,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107934096</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5943,6 +6203,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567446</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6044,6 +6309,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567766</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6142,6 +6412,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107931475</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6240,6 +6515,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107932217</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6346,6 +6626,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567432</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6452,6 +6737,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567736</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6558,6 +6848,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567775</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6664,6 +6959,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567794</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6767,6 +7067,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107926663</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6870,6 +7175,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107926893</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6978,6 +7288,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107929843</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7090,6 +7405,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930207</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7198,6 +7518,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930311</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7301,6 +7626,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930356</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7404,6 +7734,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107933310</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7507,6 +7842,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107933559</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7610,6 +7950,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107933730</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7713,6 +8058,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107933838</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7816,6 +8166,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107934086</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7919,6 +8274,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107934217</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8027,6 +8387,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107934358</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8139,6 +8504,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250170</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8251,6 +8621,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250178</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8363,6 +8738,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250180</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8475,6 +8855,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250183</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8578,6 +8963,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107932237</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8702,6 +9092,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124269609</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8815,6 +9210,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134974762</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8916,6 +9316,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567462</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9017,6 +9422,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567745</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9124,6 +9534,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107930631</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9225,6 +9640,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567759</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9326,6 +9746,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567448</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9427,6 +9852,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567460</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9528,6 +9958,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567461</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9626,6 +10061,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107931482</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9733,6 +10173,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250179</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9855,6 +10300,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113250176</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9954,6 +10404,11 @@
       <c r="AY91" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89567457</t>
         </is>
       </c>
     </row>
@@ -10091,8 +10546,106 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113292342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 10723-2023 artfynd.xlsx
+++ b/artfynd/A 10723-2023 artfynd.xlsx
@@ -9103,7 +9103,7 @@
         <v>134974762</v>
       </c>
       <c r="B80" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
